--- a/etf_holdings/2026-09-03_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:14</t>
+          <t>2026-09-03 00:51:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:16</t>
+          <t>2026-09-03 00:51:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:17</t>
+          <t>2026-09-03 00:51:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:18</t>
+          <t>2026-09-03 00:51:32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:18</t>
+          <t>2026-09-03 00:51:32</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:18</t>
+          <t>2026-09-03 00:51:32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:18</t>
+          <t>2026-09-03 00:51:32</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 00:32:18</t>
+          <t>2026-09-03 00:51:32</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:29</t>
+          <t>2026-09-03 01:12:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:29</t>
+          <t>2026-09-03 01:12:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:29</t>
+          <t>2026-09-03 01:12:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:29</t>
+          <t>2026-09-03 01:12:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:29</t>
+          <t>2026-09-03 01:12:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:29</t>
+          <t>2026-09-03 01:12:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:29</t>
+          <t>2026-09-03 01:12:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:29</t>
+          <t>2026-09-03 01:12:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:29</t>
+          <t>2026-09-03 01:12:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:29</t>
+          <t>2026-09-03 01:12:34</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:29</t>
+          <t>2026-09-03 01:12:34</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:29</t>
+          <t>2026-09-03 01:12:34</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:29</t>
+          <t>2026-09-03 01:12:34</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:29</t>
+          <t>2026-09-03 01:12:34</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:29</t>
+          <t>2026-09-03 01:12:34</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:30</t>
+          <t>2026-09-03 01:12:36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:30</t>
+          <t>2026-09-03 01:12:36</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:30</t>
+          <t>2026-09-03 01:12:36</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:30</t>
+          <t>2026-09-03 01:12:36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:30</t>
+          <t>2026-09-03 01:12:36</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:30</t>
+          <t>2026-09-03 01:12:36</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:30</t>
+          <t>2026-09-03 01:12:36</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:30</t>
+          <t>2026-09-03 01:12:36</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:30</t>
+          <t>2026-09-03 01:12:36</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:30</t>
+          <t>2026-09-03 01:12:36</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:30</t>
+          <t>2026-09-03 01:12:36</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:30</t>
+          <t>2026-09-03 01:12:36</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:30</t>
+          <t>2026-09-03 01:12:36</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:30</t>
+          <t>2026-09-03 01:12:36</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:30</t>
+          <t>2026-09-03 01:12:36</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:31</t>
+          <t>2026-09-03 01:12:37</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:31</t>
+          <t>2026-09-03 01:12:37</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:31</t>
+          <t>2026-09-03 01:12:37</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:31</t>
+          <t>2026-09-03 01:12:37</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:31</t>
+          <t>2026-09-03 01:12:37</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:31</t>
+          <t>2026-09-03 01:12:37</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:31</t>
+          <t>2026-09-03 01:12:37</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:31</t>
+          <t>2026-09-03 01:12:37</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:31</t>
+          <t>2026-09-03 01:12:37</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:31</t>
+          <t>2026-09-03 01:12:37</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:31</t>
+          <t>2026-09-03 01:12:37</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:31</t>
+          <t>2026-09-03 01:12:37</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:31</t>
+          <t>2026-09-03 01:12:37</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:31</t>
+          <t>2026-09-03 01:12:37</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:31</t>
+          <t>2026-09-03 01:12:37</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:32</t>
+          <t>2026-09-03 01:12:38</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:32</t>
+          <t>2026-09-03 01:12:38</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:32</t>
+          <t>2026-09-03 01:12:38</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:32</t>
+          <t>2026-09-03 01:12:38</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 00:51:32</t>
+          <t>2026-09-03 01:12:38</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:34</t>
+          <t>2026-09-03 21:39:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-2.25%2385</t>
+          <t>+0.21%2390</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-2.25%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2385</v>
+        <v>2390</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.23%3,800,000</t>
+          <t>11.69%3,800,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11.23%</t>
+          <t>11.69%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:34</t>
+          <t>2026-09-03 21:39:35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-3.46%5445</t>
+          <t>-2.85%5290</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5445</v>
+        <v>5290</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.31%1,380,000</t>
+          <t>9.40%1,380,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.31%</t>
+          <t>9.40%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:34</t>
+          <t>2026-09-03 21:39:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2408南亞科技</t>
+          <t>2059川湖科技</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0%518</t>
+          <t>-2.99%13450</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>518</v>
+        <v>13450</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.86%13,800,000</t>
+          <t>8.66%500,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.86%</t>
+          <t>8.66%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>13800000</v>
+        <v>500000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:34</t>
+          <t>2026-09-03 21:39:35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2059川湖科技</t>
+          <t>2408南亞科技</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.01%13865</t>
+          <t>-7.82%477.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.01%</t>
+          <t>-7.82%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>13865</v>
+        <v>477.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8.59%500,000</t>
+          <t>8.48%13,800,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.59%</t>
+          <t>8.48%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>500000</v>
+        <v>13800000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:34</t>
+          <t>2026-09-03 21:39:35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.21%973</t>
+          <t>-5.14%923</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-5.14%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>973</v>
+        <v>923</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.03%5,000,000</t>
+          <t>5.94%5,000,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.03%</t>
+          <t>5.94%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:34</t>
+          <t>2026-09-03 21:39:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0%2610</t>
+          <t>-5.17%2475</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-5.17%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2610</v>
+        <v>2475</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.60%1,730,020</t>
+          <t>5.51%1,730,020</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.60%</t>
+          <t>5.51%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:34</t>
+          <t>2026-09-03 21:39:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-2.93%3310</t>
+          <t>-0.3%3300</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3310</v>
+        <v>3300</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.13%1,250,000</t>
+          <t>5.31%1,250,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.13%</t>
+          <t>5.31%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:34</t>
+          <t>2026-09-03 21:39:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2327國巨股份</t>
+          <t>2454聯發科技</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-4.93%540</t>
+          <t>+1.52%4340</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-4.93%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>540</v>
+        <v>4340</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.02%7,500,000</t>
+          <t>5.03%900,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.02%</t>
+          <t>5.03%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>7500000</v>
+        <v>900000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:34</t>
+          <t>2026-09-03 21:39:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8046南亞電路</t>
+          <t>2327國巨股份</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.04%1200</t>
+          <t>-5.37%511</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>-5.37%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1200</v>
+        <v>511</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.83%3,250,000</t>
+          <t>4.93%7,500,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.83%</t>
+          <t>4.93%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3250000</v>
+        <v>7500000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:34</t>
+          <t>2026-09-03 21:39:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2454聯發科技</t>
+          <t>8046南亞電路</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.93%4275</t>
+          <t>-10%1080</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4275</v>
+        <v>1080</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.77%900,000</t>
+          <t>4.52%3,250,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.77%</t>
+          <t>4.52%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>900000</v>
+        <v>3250000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:34</t>
+          <t>2026-09-03 21:39:35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-3.09%847</t>
+          <t>-8.5%775</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>847</v>
+        <v>775</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.30%4,100,000</t>
+          <t>4.09%4,100,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>4.09%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:34</t>
+          <t>2026-09-03 21:39:35</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.95%2140</t>
+          <t>-2.34%2090</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2140</v>
+        <v>2090</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.85%1,450,000</t>
+          <t>3.90%1,450,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>3.90%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:34</t>
+          <t>2026-09-03 21:39:35</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.88%3395</t>
+          <t>-8.1%3120</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3395</v>
+        <v>3120</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.79%900,000</t>
+          <t>3.62%900,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>3.62%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:34</t>
+          <t>2026-09-03 21:39:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6274台燿科技</t>
+          <t>5274信驊科技</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.76%1410</t>
+          <t>+0.71%17850</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.76%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1410</v>
+        <v>17850</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.15%1,800,000</t>
+          <t>3.23%140,500</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1800000</v>
+        <v>140500</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:34</t>
+          <t>2026-09-03 21:39:35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5274信驊科技</t>
+          <t>6274台燿科技</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+3.53%17725</t>
+          <t>-4.61%1345</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+3.53%</t>
+          <t>-4.61%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>17725</v>
+        <v>1345</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.09%140,500</t>
+          <t>3.12%1,800,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>140500</v>
+        <v>1800000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:36</t>
+          <t>2026-09-03 21:39:38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.22%5290</t>
+          <t>-4.63%5045</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-4.63%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5290</v>
+        <v>5045</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.49%380,000</t>
+          <t>2.47%380,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.47%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:36</t>
+          <t>2026-09-03 21:39:38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.95%5770</t>
+          <t>-2.69%5615</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-2.69%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5770</v>
+        <v>5615</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.43%340,000</t>
+          <t>2.46%340,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.46%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:36</t>
+          <t>2026-09-03 21:39:38</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-6.16%686</t>
+          <t>-7%638</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-6.16%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>686</v>
+        <v>638</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.29%2,700,000</t>
+          <t>2.22%2,700,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:36</t>
+          <t>2026-09-03 21:39:38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8299群聯電子</t>
+          <t>7769鴻勁精密</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.82%2065</t>
+          <t>+2.8%5870</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>+2.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2065</v>
+        <v>5870</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.00%780,000</t>
+          <t>2.12%280,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>780000</v>
+        <v>280000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:36</t>
+          <t>2026-09-03 21:39:38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7769鴻勁精密</t>
+          <t>8299群聯電子</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-2.73%5710</t>
+          <t>-3.15%2000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-2.73%</t>
+          <t>-3.15%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5710</v>
+        <v>2000</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.98%280,000</t>
+          <t>2.01%780,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>280000</v>
+        <v>780000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:36</t>
+          <t>2026-09-03 21:39:38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+3.03%7810</t>
+          <t>-8.45%7150</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>-8.45%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>7810</v>
+        <v>7150</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.01%1,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:36</t>
+          <t>2026-09-03 21:39:38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-3.44%589</t>
+          <t>0%589</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-3.44%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:36</t>
+          <t>2026-09-03 21:39:38</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.46%337</t>
+          <t>-0.59%335</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:36</t>
+          <t>2026-09-03 21:39:38</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-1.95%251</t>
+          <t>-1.39%247.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>251</v>
+        <v>247.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:36</t>
+          <t>2026-09-03 21:39:38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-1.47%234.5</t>
+          <t>+1.92%239</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>234.5</v>
+        <v>239</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:36</t>
+          <t>2026-09-03 21:39:38</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-6.26%2170</t>
+          <t>-3.23%2100</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-6.26%</t>
+          <t>-3.23%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2170</v>
+        <v>2100</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:36</t>
+          <t>2026-09-03 21:39:38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.71%1975</t>
+          <t>+2.03%2015</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.71%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1975</v>
+        <v>2015</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:36</t>
+          <t>2026-09-03 21:39:38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-7.24%1730</t>
+          <t>+1.73%1760</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-7.24%</t>
+          <t>+1.73%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1730</v>
+        <v>1760</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:36</t>
+          <t>2026-09-03 21:39:38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+1.92%185.5</t>
+          <t>+1.62%188.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>+1.62%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>185.5</v>
+        <v>188.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:36</t>
+          <t>2026-09-03 21:39:38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.61%149.5</t>
+          <t>-1.67%147</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.61%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>149.5</v>
+        <v>147</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:37</t>
+          <t>2026-09-03 21:39:39</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.03%143.5</t>
+          <t>+2.44%147</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+2.44%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>143.5</v>
+        <v>147</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:37</t>
+          <t>2026-09-03 21:39:39</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-4.91%126</t>
+          <t>-0.79%125</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:37</t>
+          <t>2026-09-03 21:39:39</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,25 +2456,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2357華碩電腦</t>
+          <t>2882國泰金融</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0%1010</t>
+          <t>+3.21%112.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+3.21%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1010</v>
+        <v>112.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:37</t>
+          <t>2026-09-03 21:39:39</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,25 +2517,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2882國泰金融</t>
+          <t>2357華碩電腦</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.8%109</t>
+          <t>-3.86%971</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-3.86%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>109</v>
+        <v>971</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:37</t>
+          <t>2026-09-03 21:39:39</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0%744</t>
+          <t>-4.97%707</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.97%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>744</v>
+        <v>707</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:37</t>
+          <t>2026-09-03 21:39:39</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0%66.7</t>
+          <t>+2.7%68.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.7%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>66.7</v>
+        <v>68.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:37</t>
+          <t>2026-09-03 21:39:39</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.15%66.6</t>
+          <t>+1.35%67.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+1.35%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>66.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:37</t>
+          <t>2026-09-03 21:39:39</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.2%502</t>
+          <t>-2.89%487.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>502</v>
+        <v>487.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:37</t>
+          <t>2026-09-03 21:39:39</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,21 +2822,21 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2886兆豐金融</t>
+          <t>2884玉山金融</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+1.03%49</t>
+          <t>+6.67%43.2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>+6.67%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>49</v>
+        <v>43.2</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:37</t>
+          <t>2026-09-03 21:39:39</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,30 +2883,30 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2887台新新光</t>
+          <t>2886兆豐金融</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+2.23%41.2</t>
+          <t>+2.86%50.4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+2.23%</t>
+          <t>+2.86%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>41.2</v>
+        <v>50.4</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:37</t>
+          <t>2026-09-03 21:39:39</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,34 +2944,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2890永豐金融</t>
+          <t>2880華南金融</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+1.57%42.15</t>
+          <t>+1.05%43.45</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>42.15</v>
+        <v>43.45</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>&lt;0.01%9,090</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>9000</v>
+        <v>9090</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:37</t>
+          <t>2026-09-03 21:39:39</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,25 +3005,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2880華南金融</t>
+          <t>2883凱基金融</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+2.5%43</t>
+          <t>+1.13%35.9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>43</v>
+        <v>35.9</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0%9,090</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>9090</v>
+        <v>9000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:37</t>
+          <t>2026-09-03 21:39:39</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,25 +3066,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>2887台新新光</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-3.05%270.5</t>
+          <t>+0.61%41.45</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-3.05%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>270.5</v>
+        <v>41.45</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0%1,450</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>1450</v>
+        <v>9000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:37</t>
+          <t>2026-09-03 21:39:39</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,21 +3127,21 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2884玉山金融</t>
+          <t>2890永豐金融</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+1.5%40.5</t>
+          <t>+1.07%42.6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.5%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>40.5</v>
+        <v>42.6</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:37</t>
+          <t>2026-09-03 21:39:39</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,25 +3188,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2883凱基金融</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+1.57%35.5</t>
+          <t>-3.51%261</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>35.5</v>
+        <v>261</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,450</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>9000</v>
+        <v>1450</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:38</t>
+          <t>2026-09-03 21:39:40</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.19%249</t>
+          <t>-5.22%236</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>-5.22%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:38</t>
+          <t>2026-09-03 21:39:40</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.46%217</t>
+          <t>-0.23%216.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>217</v>
+        <v>216.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:38</t>
+          <t>2026-09-03 21:39:40</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-4.59%187</t>
+          <t>+1.87%190.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-4.59%</t>
+          <t>+1.87%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>187</v>
+        <v>190.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:38</t>
+          <t>2026-09-03 21:39:40</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+1.1%137.5</t>
+          <t>+0.36%138</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>137.5</v>
+        <v>138</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:38</t>
+          <t>2026-09-03 21:39:40</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+0.52%76.6</t>
+          <t>-1.31%75.6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>76.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-03_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:35</t>
+          <t>2026-09-03 21:55:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:35</t>
+          <t>2026-09-03 21:55:31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:35</t>
+          <t>2026-09-03 21:55:31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:35</t>
+          <t>2026-09-03 21:55:31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:35</t>
+          <t>2026-09-03 21:55:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:35</t>
+          <t>2026-09-03 21:55:31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:35</t>
+          <t>2026-09-03 21:55:31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:35</t>
+          <t>2026-09-03 21:55:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:35</t>
+          <t>2026-09-03 21:55:31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:35</t>
+          <t>2026-09-03 21:55:31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:35</t>
+          <t>2026-09-03 21:55:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:35</t>
+          <t>2026-09-03 21:55:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:35</t>
+          <t>2026-09-03 21:55:31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:35</t>
+          <t>2026-09-03 21:55:31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:35</t>
+          <t>2026-09-03 21:55:31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:38</t>
+          <t>2026-09-03 21:55:32</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:38</t>
+          <t>2026-09-03 21:55:32</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:38</t>
+          <t>2026-09-03 21:55:32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:38</t>
+          <t>2026-09-03 21:55:32</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:38</t>
+          <t>2026-09-03 21:55:32</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:38</t>
+          <t>2026-09-03 21:55:32</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:38</t>
+          <t>2026-09-03 21:55:32</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:38</t>
+          <t>2026-09-03 21:55:32</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:38</t>
+          <t>2026-09-03 21:55:32</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:38</t>
+          <t>2026-09-03 21:55:32</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:38</t>
+          <t>2026-09-03 21:55:32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:38</t>
+          <t>2026-09-03 21:55:32</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:38</t>
+          <t>2026-09-03 21:55:32</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:38</t>
+          <t>2026-09-03 21:55:32</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:38</t>
+          <t>2026-09-03 21:55:32</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:39</t>
+          <t>2026-09-03 21:55:33</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:39</t>
+          <t>2026-09-03 21:55:33</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:39</t>
+          <t>2026-09-03 21:55:33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:39</t>
+          <t>2026-09-03 21:55:33</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:39</t>
+          <t>2026-09-03 21:55:33</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:39</t>
+          <t>2026-09-03 21:55:33</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:39</t>
+          <t>2026-09-03 21:55:33</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:39</t>
+          <t>2026-09-03 21:55:33</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:39</t>
+          <t>2026-09-03 21:55:33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:39</t>
+          <t>2026-09-03 21:55:33</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:39</t>
+          <t>2026-09-03 21:55:33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:39</t>
+          <t>2026-09-03 21:55:33</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:39</t>
+          <t>2026-09-03 21:55:33</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:39</t>
+          <t>2026-09-03 21:55:33</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:39</t>
+          <t>2026-09-03 21:55:33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:40</t>
+          <t>2026-09-03 21:55:34</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:40</t>
+          <t>2026-09-03 21:55:34</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:40</t>
+          <t>2026-09-03 21:55:34</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:40</t>
+          <t>2026-09-03 21:55:34</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:40</t>
+          <t>2026-09-03 21:55:34</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:31</t>
+          <t>2026-09-03 22:30:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:31</t>
+          <t>2026-09-03 22:30:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:31</t>
+          <t>2026-09-03 22:30:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:31</t>
+          <t>2026-09-03 22:30:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:31</t>
+          <t>2026-09-03 22:30:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:31</t>
+          <t>2026-09-03 22:30:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:31</t>
+          <t>2026-09-03 22:30:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:31</t>
+          <t>2026-09-03 22:30:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:31</t>
+          <t>2026-09-03 22:30:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:31</t>
+          <t>2026-09-03 22:30:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:31</t>
+          <t>2026-09-03 22:30:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:31</t>
+          <t>2026-09-03 22:30:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:31</t>
+          <t>2026-09-03 22:30:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:31</t>
+          <t>2026-09-03 22:30:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:31</t>
+          <t>2026-09-03 22:30:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:32</t>
+          <t>2026-09-03 22:30:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:32</t>
+          <t>2026-09-03 22:30:55</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:32</t>
+          <t>2026-09-03 22:30:55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:32</t>
+          <t>2026-09-03 22:30:55</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:32</t>
+          <t>2026-09-03 22:30:55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:32</t>
+          <t>2026-09-03 22:30:55</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:32</t>
+          <t>2026-09-03 22:30:55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:32</t>
+          <t>2026-09-03 22:30:55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:32</t>
+          <t>2026-09-03 22:30:55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:32</t>
+          <t>2026-09-03 22:30:55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:32</t>
+          <t>2026-09-03 22:30:55</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:32</t>
+          <t>2026-09-03 22:30:55</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:32</t>
+          <t>2026-09-03 22:30:55</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:32</t>
+          <t>2026-09-03 22:30:55</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:32</t>
+          <t>2026-09-03 22:30:55</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:33</t>
+          <t>2026-09-03 22:30:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:33</t>
+          <t>2026-09-03 22:30:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:33</t>
+          <t>2026-09-03 22:30:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:33</t>
+          <t>2026-09-03 22:30:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:33</t>
+          <t>2026-09-03 22:30:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:33</t>
+          <t>2026-09-03 22:30:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:33</t>
+          <t>2026-09-03 22:30:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:33</t>
+          <t>2026-09-03 22:30:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:33</t>
+          <t>2026-09-03 22:30:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:33</t>
+          <t>2026-09-03 22:30:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:33</t>
+          <t>2026-09-03 22:30:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:33</t>
+          <t>2026-09-03 22:30:56</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:33</t>
+          <t>2026-09-03 22:30:56</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:33</t>
+          <t>2026-09-03 22:30:56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:33</t>
+          <t>2026-09-03 22:30:56</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:34</t>
+          <t>2026-09-03 22:30:57</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:34</t>
+          <t>2026-09-03 22:30:57</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:34</t>
+          <t>2026-09-03 22:30:57</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:34</t>
+          <t>2026-09-03 22:30:57</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:34</t>
+          <t>2026-09-03 22:30:57</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:53</t>
+          <t>2026-09-03 22:44:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:53</t>
+          <t>2026-09-03 22:44:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:53</t>
+          <t>2026-09-03 22:44:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:53</t>
+          <t>2026-09-03 22:44:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:53</t>
+          <t>2026-09-03 22:44:11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:53</t>
+          <t>2026-09-03 22:44:11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:53</t>
+          <t>2026-09-03 22:44:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:53</t>
+          <t>2026-09-03 22:44:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:53</t>
+          <t>2026-09-03 22:44:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:53</t>
+          <t>2026-09-03 22:44:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:53</t>
+          <t>2026-09-03 22:44:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:53</t>
+          <t>2026-09-03 22:44:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:53</t>
+          <t>2026-09-03 22:44:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:53</t>
+          <t>2026-09-03 22:44:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:53</t>
+          <t>2026-09-03 22:44:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:55</t>
+          <t>2026-09-03 22:44:12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:55</t>
+          <t>2026-09-03 22:44:12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:55</t>
+          <t>2026-09-03 22:44:12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:55</t>
+          <t>2026-09-03 22:44:12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:55</t>
+          <t>2026-09-03 22:44:12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:55</t>
+          <t>2026-09-03 22:44:12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:55</t>
+          <t>2026-09-03 22:44:12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:55</t>
+          <t>2026-09-03 22:44:12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:55</t>
+          <t>2026-09-03 22:44:12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:55</t>
+          <t>2026-09-03 22:44:12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:55</t>
+          <t>2026-09-03 22:44:12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:55</t>
+          <t>2026-09-03 22:44:12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:55</t>
+          <t>2026-09-03 22:44:12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:55</t>
+          <t>2026-09-03 22:44:12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:55</t>
+          <t>2026-09-03 22:44:12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:56</t>
+          <t>2026-09-03 22:44:13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:56</t>
+          <t>2026-09-03 22:44:13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:56</t>
+          <t>2026-09-03 22:44:13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:56</t>
+          <t>2026-09-03 22:44:13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:56</t>
+          <t>2026-09-03 22:44:13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:56</t>
+          <t>2026-09-03 22:44:13</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:56</t>
+          <t>2026-09-03 22:44:13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:56</t>
+          <t>2026-09-03 22:44:13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:56</t>
+          <t>2026-09-03 22:44:13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:56</t>
+          <t>2026-09-03 22:44:13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:56</t>
+          <t>2026-09-03 22:44:13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:56</t>
+          <t>2026-09-03 22:44:13</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:56</t>
+          <t>2026-09-03 22:44:13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:56</t>
+          <t>2026-09-03 22:44:13</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:56</t>
+          <t>2026-09-03 22:44:13</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:57</t>
+          <t>2026-09-03 22:44:14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:57</t>
+          <t>2026-09-03 22:44:14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:57</t>
+          <t>2026-09-03 22:44:14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:57</t>
+          <t>2026-09-03 22:44:14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:57</t>
+          <t>2026-09-03 22:44:14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:11</t>
+          <t>2026-09-03 22:59:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:12</t>
+          <t>2026-09-03 22:59:55</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:13</t>
+          <t>2026-09-03 22:59:56</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:14</t>
+          <t>2026-09-03 22:59:57</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:14</t>
+          <t>2026-09-03 22:59:57</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:14</t>
+          <t>2026-09-03 22:59:57</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:14</t>
+          <t>2026-09-03 22:59:57</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:14</t>
+          <t>2026-09-03 22:59:57</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
